--- a/engine/scem_study/SCEM_Valuation_Model_10092026_public.xlsx
+++ b/engine/scem_study/SCEM_Valuation_Model_10092026_public.xlsx
@@ -2270,19 +2270,19 @@
         </is>
       </c>
       <c r="D5" s="18" t="n">
-        <v>62.1420635589089</v>
+        <v>62.56105027078401</v>
       </c>
       <c r="E5" s="18" t="n">
-        <v>72.94331198622631</v>
+        <v>73.49898389243793</v>
       </c>
       <c r="F5" s="18" t="n">
-        <v>80.17497538017265</v>
+        <v>80.4686077465383</v>
       </c>
       <c r="G5" s="18" t="n">
-        <v>88.18397736359992</v>
+        <v>88.1033152937333</v>
       </c>
       <c r="H5" s="18" t="n">
-        <v>103.4995013727537</v>
+        <v>103.4660978622792</v>
       </c>
     </row>
     <row r="6">
@@ -2300,19 +2300,19 @@
         </is>
       </c>
       <c r="D6" s="18" t="n">
-        <v>52.12577688877463</v>
+        <v>52.88504636212016</v>
       </c>
       <c r="E6" s="18" t="n">
-        <v>69.74973064913542</v>
+        <v>70.74037129421815</v>
       </c>
       <c r="F6" s="18" t="n">
-        <v>82.77876151400348</v>
+        <v>83.30649231353813</v>
       </c>
       <c r="G6" s="18" t="n">
-        <v>98.07395179014382</v>
+        <v>98.10001046745072</v>
       </c>
       <c r="H6" s="18" t="n">
-        <v>131.3522656071748</v>
+        <v>130.9274713339168</v>
       </c>
     </row>
     <row r="8">
@@ -2350,19 +2350,19 @@
         </is>
       </c>
       <c r="B9" s="20" t="n">
-        <v>0.54204</v>
+        <v>0.5556</v>
       </c>
       <c r="C9" s="20" t="n">
-        <v>0.2819</v>
+        <v>0.28202</v>
       </c>
       <c r="D9" s="20" t="n">
-        <v>0.19682</v>
+        <v>0.1826</v>
       </c>
       <c r="E9" s="20" t="n">
-        <v>0.4586</v>
+        <v>0.45358</v>
       </c>
       <c r="F9" s="20" t="n">
-        <v>0.35234</v>
+        <v>0.32974</v>
       </c>
     </row>
     <row r="10">
@@ -2372,19 +2372,19 @@
         </is>
       </c>
       <c r="B10" s="20" t="n">
-        <v>0.5746599999999999</v>
+        <v>0.58796</v>
       </c>
       <c r="C10" s="20" t="n">
-        <v>0.4217</v>
+        <v>0.42856</v>
       </c>
       <c r="D10" s="20" t="n">
-        <v>0.27342</v>
+        <v>0.25652</v>
       </c>
       <c r="E10" s="20" t="n">
-        <v>0.70524</v>
+        <v>0.704</v>
       </c>
       <c r="F10" s="20" t="n">
-        <v>0.56498</v>
+        <v>0.54084</v>
       </c>
     </row>
     <row r="12">

--- a/engine/scem_study/SCEM_Valuation_Model_10092026_public.xlsx
+++ b/engine/scem_study/SCEM_Valuation_Model_10092026_public.xlsx
@@ -2553,19 +2553,19 @@
         <v>0.2595969690413578</v>
       </c>
       <c r="B6" s="18" t="n">
-        <v>105.2712424795545</v>
+        <v>111.2500289678406</v>
       </c>
       <c r="C6" s="18" t="n">
-        <v>109.3054795323648</v>
+        <v>116.1599922586754</v>
       </c>
       <c r="D6" s="18" t="n">
-        <v>113.9891474702462</v>
+        <v>121.9456358687676</v>
       </c>
       <c r="E6" s="18" t="n">
-        <v>119.4934056037856</v>
+        <v>128.8649448441618</v>
       </c>
       <c r="F6" s="18" t="n">
-        <v>126.0553520425674</v>
+        <v>137.2882802768256</v>
       </c>
     </row>
     <row r="7">
@@ -2573,19 +2573,19 @@
         <v>0.2745969690413578</v>
       </c>
       <c r="B7" s="18" t="n">
-        <v>103.9470986180909</v>
+        <v>109.8088132858434</v>
       </c>
       <c r="C7" s="18" t="n">
-        <v>107.9054278920373</v>
+        <v>114.6260464788476</v>
       </c>
       <c r="D7" s="18" t="n">
-        <v>112.5009684280218</v>
+        <v>120.3024217978756</v>
       </c>
       <c r="E7" s="18" t="n">
-        <v>117.9016590210968</v>
+        <v>127.0910519554858</v>
       </c>
       <c r="F7" s="18" t="n">
-        <v>124.3401365678251</v>
+        <v>135.3553033640002</v>
       </c>
     </row>
     <row r="8">
@@ -2593,19 +2593,19 @@
         <v>0.2895969690413578</v>
       </c>
       <c r="B8" s="18" t="n">
-        <v>102.6563536606548</v>
+        <v>108.4041448401097</v>
       </c>
       <c r="C8" s="18" t="n">
-        <v>106.5407519781437</v>
+        <v>113.1310702318159</v>
       </c>
       <c r="D8" s="18" t="n">
-        <v>111.0504601632167</v>
+        <v>118.7010315671598</v>
       </c>
       <c r="E8" s="18" t="n">
-        <v>116.3502803654162</v>
+        <v>125.3623965003568</v>
       </c>
       <c r="F8" s="18" t="n">
-        <v>122.6685044490754</v>
+        <v>133.4717194791743</v>
       </c>
     </row>
     <row r="9">
@@ -2613,19 +2613,19 @@
         <v>0.3045969690413578</v>
       </c>
       <c r="B9" s="18" t="n">
-        <v>101.3978911977065</v>
+        <v>107.034797834607</v>
       </c>
       <c r="C9" s="18" t="n">
-        <v>105.2102684190301</v>
+        <v>111.6737554684416</v>
       </c>
       <c r="D9" s="18" t="n">
-        <v>109.6363615625115</v>
+        <v>117.1400602047283</v>
       </c>
       <c r="E9" s="18" t="n">
-        <v>114.837917161227</v>
+        <v>123.677457592644</v>
       </c>
       <c r="F9" s="18" t="n">
-        <v>121.0389942926093</v>
+        <v>131.6358666260975</v>
       </c>
     </row>
     <row r="10">
@@ -2633,19 +2633,19 @@
         <v>0.3195969690413578</v>
       </c>
       <c r="B10" s="18" t="n">
-        <v>100.1706416524464</v>
+        <v>105.6995980142639</v>
       </c>
       <c r="C10" s="18" t="n">
-        <v>103.9128435020293</v>
+        <v>110.2528491588272</v>
       </c>
       <c r="D10" s="18" t="n">
-        <v>108.2574644527894</v>
+        <v>115.6181618565539</v>
       </c>
       <c r="E10" s="18" t="n">
-        <v>113.3632737293079</v>
+        <v>122.0347783658078</v>
       </c>
       <c r="F10" s="18" t="n">
-        <v>119.4502060980856</v>
+        <v>129.8461527953091</v>
       </c>
     </row>
     <row r="12">
@@ -2690,19 +2690,19 @@
         </is>
       </c>
       <c r="B14" s="18" t="n">
-        <v>116.9172458541885</v>
+        <v>127.7204608842874</v>
       </c>
       <c r="C14" s="18" t="n">
-        <v>119.792875151632</v>
+        <v>130.5960901817308</v>
       </c>
       <c r="D14" s="18" t="n">
-        <v>122.6685044490754</v>
+        <v>133.4717194791743</v>
       </c>
       <c r="E14" s="18" t="n">
-        <v>125.5441337465189</v>
+        <v>136.3473487766178</v>
       </c>
       <c r="F14" s="18" t="n">
-        <v>128.4197630439624</v>
+        <v>139.2229780740612</v>
       </c>
     </row>
     <row r="16">
@@ -2761,19 +2761,19 @@
         </is>
       </c>
       <c r="B22" s="18" t="n">
-        <v>157.9026265409939</v>
+        <v>179.7587426418379</v>
       </c>
       <c r="C22" s="18" t="n">
-        <v>156.8570192056681</v>
+        <v>178.3207960113649</v>
       </c>
       <c r="D22" s="18" t="n">
-        <v>137.2220532144429</v>
+        <v>152.0630000003824</v>
       </c>
       <c r="E22" s="18" t="n">
-        <v>122.6685044490754</v>
+        <v>133.4717194791743</v>
       </c>
       <c r="F22" s="18" t="n">
-        <v>106.7727176961527</v>
+        <v>113.9600805321782</v>
       </c>
     </row>
     <row r="24">
@@ -2818,19 +2818,19 @@
         </is>
       </c>
       <c r="B26" s="18" t="n">
-        <v>109.2573175378658</v>
+        <v>118.6101014667924</v>
       </c>
       <c r="C26" s="18" t="n">
-        <v>115.9629109934706</v>
+        <v>126.0409104729834</v>
       </c>
       <c r="D26" s="18" t="n">
-        <v>122.6685044490754</v>
+        <v>133.4717194791743</v>
       </c>
       <c r="E26" s="18" t="n">
-        <v>129.3740979046802</v>
+        <v>140.9025284853652</v>
       </c>
       <c r="F26" s="18" t="n">
-        <v>136.0796913602851</v>
+        <v>148.3333374915562</v>
       </c>
     </row>
     <row r="28">
@@ -4844,7 +4844,7 @@
         </is>
       </c>
       <c r="B51" s="24" t="n">
-        <v>0.105</v>
+        <v>0.09000000000000001</v>
       </c>
     </row>
     <row r="52">
@@ -5194,7 +5194,7 @@
         </is>
       </c>
       <c r="B87" s="18" t="n">
-        <v>22.29436104663261</v>
+        <v>22.24202836806915</v>
       </c>
     </row>
     <row r="88">
@@ -5204,7 +5204,7 @@
         </is>
       </c>
       <c r="B88" s="18" t="n">
-        <v>95.67157376888532</v>
+        <v>100.8571169833328</v>
       </c>
     </row>
     <row r="89">
